--- a/Config/GameConfig/Datas/__tables__.xlsx
+++ b/Config/GameConfig/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C2B9CF-EC0D-4111-A012-E9C585C0CDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663B1856-21AE-49ED-BD4F-92BBA272B88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,245 +20,305 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
   <si>
     <t>##var</t>
   </si>
   <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>mode</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>output</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>全名(包含模块和名字)</t>
+  </si>
+  <si>
+    <t>记录类名</t>
+  </si>
+  <si>
+    <t>从excel读取定义</t>
+  </si>
+  <si>
+    <t>文件列表</t>
+  </si>
+  <si>
+    <t>表id字段</t>
+  </si>
+  <si>
+    <t>模式</t>
+  </si>
+  <si>
+    <t>分组</t>
+  </si>
+  <si>
+    <t>注释</t>
+  </si>
+  <si>
+    <t>输出文件名</t>
+  </si>
+  <si>
+    <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
+  </si>
+  <si>
+    <t>可以多个，以逗号','分隔</t>
+  </si>
+  <si>
+    <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
+  </si>
+  <si>
+    <t>取值one|map|list，为空自动为map</t>
+  </si>
+  <si>
+    <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
+  </si>
+  <si>
+    <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>Worker</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>worker.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character.TbWorker</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbForniture</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>forniture.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbCrops</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crops</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>crops.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbLivestock</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Livestock</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>livestock.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbFish</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fish</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fish.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbSeasoning</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seasoning</t>
+  </si>
+  <si>
+    <t>调味品</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>雇员</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>农作物</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>牲畜</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼类</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>seasoning.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbRanchProduct</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RanchProduct</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ranchproduct.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>牧场产物(肉类和副产品)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>site.TbFarmlandUnlock</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FarmlandUnlock</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>farmlandUnlock.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>农场田地解锁条件</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbCommonItem</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forniture</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CommonItem</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonItem.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用道具</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>network.TbErrorCode</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ErrorCode</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>errorcode.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>resp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayModule</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>module.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>common.TbModule</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>global.TbGlobal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Global</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>global.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>one</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>全局</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>site.TbFarmlandChangeType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FarmlandChangeType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>farmlandChangeType.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>value_type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>full_name</t>
-  </si>
-  <si>
-    <t>value_type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>read_schema_from_file</t>
-  </si>
-  <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>mode</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>tags</t>
-  </si>
-  <si>
-    <t>output</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>记录类名</t>
-  </si>
-  <si>
-    <t>从excel读取定义</t>
-  </si>
-  <si>
-    <t>文件列表</t>
-  </si>
-  <si>
-    <t>表id字段</t>
-  </si>
-  <si>
-    <t>模式</t>
-  </si>
-  <si>
-    <t>分组</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>输出文件名</t>
-  </si>
-  <si>
-    <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
-  </si>
-  <si>
-    <t>可以多个，以逗号','分隔</t>
-  </si>
-  <si>
-    <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
-  </si>
-  <si>
-    <t>取值one|map|list，为空自动为map</t>
-  </si>
-  <si>
-    <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
-  </si>
-  <si>
-    <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>Worker</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>worker.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>character.TbWorker</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>item.TbForniture</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>forniture.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>item.TbCrops</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Crops</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>crops.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>item.TbLivestock</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Livestock</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>livestock.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>item.TbFish</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fish</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fish.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>item.TbSeasoning</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Seasoning</t>
-  </si>
-  <si>
-    <t>调味品</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>雇员</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>家具</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>农作物</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>牲畜</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>鱼类</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>seasoning.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>item.TbRanchProduct</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>RanchProduct</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ranchproduct.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>牧场产物(肉类和副产品)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>site.TbFarmlandUnlock</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FarmlandUnlock</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>farmlandUnlock.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>农场田地解锁条件</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>item.TbCommonItem</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Forniture</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CommonItem</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonItem.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用道具</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>network.TbErrorCode</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ErrorCode</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>errorcode.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>resp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbItemBase</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemBase</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>itemBase.xlsx</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -623,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34.625" customWidth="1"/>
@@ -641,225 +701,229 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>28</v>
+        <v>68</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>33</v>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>46</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>51</v>
+        <v>34</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>60</v>
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>62</v>
+        <v>45</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -867,33 +931,92 @@
         <v>54</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>66</v>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Config/GameConfig/Datas/__tables__.xlsx
+++ b/Config/GameConfig/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663B1856-21AE-49ED-BD4F-92BBA272B88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A36CF3-CECD-45F1-8295-1B4610168893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="96">
   <si>
     <t>##var</t>
   </si>
@@ -119,10 +119,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>crops.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>item.TbLivestock</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -131,10 +127,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>livestock.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>item.TbFish</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -143,10 +135,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>fish.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>item.TbSeasoning</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -190,10 +178,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ranchproduct.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>牧场产物(肉类和副产品)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -206,10 +190,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>farmlandUnlock.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>农场田地解锁条件</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -290,10 +270,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>farmlandChangeType.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>value_type</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -318,7 +294,91 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>itemBase.xlsx</t>
+    <t>Base/itemBase.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbSeed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbCub</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cub</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbByProduct</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByProduct</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbFry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbFishProduct</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FishProduct</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>farmland/farmlandChangeType.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>farmland/farmlandUnlock.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>farmland/crops.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>farmland/seed.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ranchland/cub.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ranchland/livestock.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ranchland/ranchproduct.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ranchland/byproduct.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fishland/fry.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fishland/fish.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fishland/fishproduct.xlsx</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -683,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34.625" customWidth="1"/>
@@ -701,13 +761,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -725,7 +785,7 @@
         <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>6</v>
@@ -788,236 +848,306 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="2"/>
+        <v>65</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="D7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>47</v>
+        <v>66</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>49</v>
+      <c r="E10" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
+        <v>46</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>58</v>
+        <v>86</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B15" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D17" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B28" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J34" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/Config/GameConfig/Datas/__tables__.xlsx
+++ b/Config/GameConfig/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A36CF3-CECD-45F1-8295-1B4610168893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F2E5E1-0793-4987-813A-8107E5A4A41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="102">
   <si>
     <t>##var</t>
   </si>
@@ -262,14 +262,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>site.TbFarmlandChangeType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FarmlandChangeType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>value_type</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -338,10 +330,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>farmland/farmlandChangeType.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>farmland/farmlandUnlock.xlsx</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -379,6 +367,42 @@
   </si>
   <si>
     <t>fishland/fishproduct.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>site.TbFarmlandType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FarmlandType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>farmland/farmlandType.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbFertilizer</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fertilizer</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>farmland/fertilizer.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Depester</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>farmland/depester.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.TbDepester</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -743,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34.625" customWidth="1"/>
@@ -761,13 +785,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -785,7 +809,7 @@
         <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>6</v>
@@ -868,16 +892,16 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -899,16 +923,16 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -922,7 +946,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>48</v>
@@ -970,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>39</v>
@@ -978,176 +1002,204 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B19" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B21" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D17" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="D21" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>45</v>
+      <c r="E21" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>80</v>
+        <v>30</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>92</v>
+      <c r="E22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D26" t="b">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B28" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C30" t="s">
         <v>35</v>
       </c>
-      <c r="D28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3" t="s">
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J34" s="2"/>
+      <c r="J36" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
